--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,6 +1155,109 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114733632</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78446</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ängena, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>404181</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7015570</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>126983506</v>
       </c>
       <c r="B8" t="n">
-        <v>80049</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>126983496</v>
       </c>
       <c r="B9" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>126983499</v>
       </c>
       <c r="B11" t="n">
-        <v>97445</v>
+        <v>97520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>126983506</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>126983496</v>
       </c>
       <c r="B9" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>126983499</v>
       </c>
       <c r="B11" t="n">
-        <v>97520</v>
+        <v>97526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>126983496</v>
       </c>
       <c r="B9" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>126983499</v>
       </c>
       <c r="B11" t="n">
-        <v>97526</v>
+        <v>97527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1260,42 +1260,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126983497</v>
+        <v>126983506</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405112</v>
+        <v>405097</v>
       </c>
       <c r="R7" t="n">
-        <v>7015557</v>
+        <v>7015361</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,6 +1342,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,32 +1361,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126983506</v>
+        <v>126983496</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>91344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229748</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1403,13 +1399,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405097</v>
+        <v>405112</v>
       </c>
       <c r="R8" t="n">
-        <v>7015361</v>
+        <v>7015557</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,37 +1462,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126983496</v>
+        <v>126983499</v>
       </c>
       <c r="B9" t="n">
-        <v>91344</v>
+        <v>97527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220686</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1567,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126983508</v>
+        <v>126983497</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1610,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405097</v>
+        <v>405112</v>
       </c>
       <c r="R10" t="n">
-        <v>7015361</v>
+        <v>7015557</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,38 +1669,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126983499</v>
+        <v>126983508</v>
       </c>
       <c r="B11" t="n">
-        <v>97527</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220686</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1711,13 +1712,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405112</v>
+        <v>405097</v>
       </c>
       <c r="R11" t="n">
-        <v>7015557</v>
+        <v>7015361</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,7 +1756,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>126983506</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>126983496</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>126983499</v>
       </c>
       <c r="B9" t="n">
-        <v>97527</v>
+        <v>97531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126983497</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126983508</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>126983506</v>
       </c>
       <c r="B7" t="n">
-        <v>80087</v>
+        <v>80089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>126983496</v>
       </c>
       <c r="B8" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>126983499</v>
       </c>
       <c r="B9" t="n">
-        <v>97531</v>
+        <v>97533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126983497</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126983508</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>126983497</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126983508</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>126983497</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>126983508</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20644-2021 artfynd.xlsx
+++ b/artfynd/A 20644-2021 artfynd.xlsx
@@ -1260,37 +1260,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126983506</v>
+        <v>126983497</v>
       </c>
       <c r="B7" t="n">
-        <v>80089</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,13 +1303,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405097</v>
+        <v>405112</v>
       </c>
       <c r="R7" t="n">
-        <v>7015361</v>
+        <v>7015557</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1347,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1361,32 +1365,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126983496</v>
+        <v>126983506</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,13 +1403,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405112</v>
+        <v>405097</v>
       </c>
       <c r="R8" t="n">
-        <v>7015557</v>
+        <v>7015361</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,38 +1466,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126983499</v>
+        <v>126983496</v>
       </c>
       <c r="B9" t="n">
-        <v>97533</v>
+        <v>91337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220686</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1564,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126983497</v>
+        <v>126983508</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1607,13 +1610,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405112</v>
+        <v>405097</v>
       </c>
       <c r="R10" t="n">
-        <v>7015557</v>
+        <v>7015361</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,42 +1672,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126983508</v>
+        <v>126983499</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>97520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1712,13 +1711,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405097</v>
+        <v>405112</v>
       </c>
       <c r="R11" t="n">
-        <v>7015361</v>
+        <v>7015557</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,6 +1755,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
